--- a/data/processed/positivacao/2024-01_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-01_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25829,7 +25829,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B981" t="inlineStr"/>
@@ -36921,7 +36921,7 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr"/>
@@ -65735,7 +65735,7 @@
     <row r="2517">
       <c r="A2517" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2517" t="inlineStr"/>
@@ -67406,12 +67406,12 @@
       <c r="A2582" t="inlineStr"/>
       <c r="B2582" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 5 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 6.293,68
+          <t>Vendedor 1 - VENDEDOR 01: positivou 5 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 6.293,68
 Vendedor 18 - LOJA: positivou 148 cliente(s), não positivou 734 cliente(s) - Total vendido: R$ 55.335,48
-Vendedor 3 - FERNANDA: positivou 97 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 161.247,66
-Vendedor 4 - DANIELA: positivou 92 cliente(s), não positivou 572 cliente(s) - Total vendido: R$ 43.068,08
+Vendedor 3 - VENDEDOR 03: positivou 97 cliente(s), não positivou 329 cliente(s) - Total vendido: R$ 161.247,66
+Vendedor 4 - VENDEDOR 04: positivou 92 cliente(s), não positivou 572 cliente(s) - Total vendido: R$ 43.068,08
 Vendedor 5 - SITE: positivou 7 cliente(s), não positivou 436 cliente(s) - Total vendido: R$ 742,92
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2582" t="inlineStr"/>
